--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13901" uniqueCount="1008">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13902" uniqueCount="1007">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2869,9 +2869,6 @@
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire/professionMedecin.code.coding:savoirFaire</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-vs-savoir-faire-profession-medecin</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire/professionMedecin.code.coding:typeSavoirFaire</t>
@@ -39063,11 +39060,13 @@
         <v>84</v>
       </c>
       <c r="X265" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y265" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y265" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z265" t="s" s="2">
-        <v>923</v>
+        <v>84</v>
       </c>
       <c r="AA265" t="s" s="2">
         <v>84</v>
@@ -39135,7 +39134,7 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>809</v>
@@ -39204,7 +39203,7 @@
       </c>
       <c r="Y266" s="2"/>
       <c r="Z266" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="AA266" t="s" s="2">
         <v>84</v>
@@ -39272,7 +39271,7 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>824</v>
@@ -39409,7 +39408,7 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>743</v>
@@ -39544,7 +39543,7 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>749</v>
@@ -39677,13 +39676,13 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>715</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D270" t="s" s="2">
         <v>84</v>
@@ -39708,7 +39707,7 @@
         <v>716</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="M270" t="s" s="2">
         <v>718</v>
@@ -39812,7 +39811,7 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>723</v>
@@ -39945,7 +39944,7 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>724</v>
@@ -40080,7 +40079,7 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>725</v>
@@ -40217,7 +40216,7 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>730</v>
@@ -40352,7 +40351,7 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>736</v>
@@ -40485,7 +40484,7 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>805</v>
@@ -40618,7 +40617,7 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>807</v>
@@ -40753,7 +40752,7 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B278" t="s" s="2">
         <v>809</v>
@@ -40888,7 +40887,7 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B279" t="s" s="2">
         <v>809</v>
@@ -40957,7 +40956,7 @@
       </c>
       <c r="Y279" s="2"/>
       <c r="Z279" t="s" s="2">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="AA279" t="s" s="2">
         <v>84</v>
@@ -41025,7 +41024,7 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B280" t="s" s="2">
         <v>809</v>
@@ -41094,7 +41093,7 @@
       </c>
       <c r="Y280" s="2"/>
       <c r="Z280" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="AA280" t="s" s="2">
         <v>84</v>
@@ -41162,7 +41161,7 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B281" t="s" s="2">
         <v>824</v>
@@ -41299,7 +41298,7 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>743</v>
@@ -41434,7 +41433,7 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B283" t="s" s="2">
         <v>749</v>
@@ -41567,13 +41566,13 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>715</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="D284" t="s" s="2">
         <v>84</v>
@@ -41598,7 +41597,7 @@
         <v>716</v>
       </c>
       <c r="L284" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="M284" t="s" s="2">
         <v>718</v>
@@ -41702,7 +41701,7 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>723</v>
@@ -41835,7 +41834,7 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B286" t="s" s="2">
         <v>724</v>
@@ -41970,7 +41969,7 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>725</v>
@@ -42107,7 +42106,7 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>730</v>
@@ -42242,7 +42241,7 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>736</v>
@@ -42375,7 +42374,7 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>805</v>
@@ -42508,7 +42507,7 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>807</v>
@@ -42643,7 +42642,7 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>809</v>
@@ -42778,7 +42777,7 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>809</v>
@@ -42847,7 +42846,7 @@
       </c>
       <c r="Y293" s="2"/>
       <c r="Z293" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="AA293" t="s" s="2">
         <v>84</v>
@@ -42915,7 +42914,7 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>809</v>
@@ -42984,7 +42983,7 @@
       </c>
       <c r="Y294" s="2"/>
       <c r="Z294" t="s" s="2">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="AA294" t="s" s="2">
         <v>84</v>
@@ -43052,7 +43051,7 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>824</v>
@@ -43189,7 +43188,7 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B296" t="s" s="2">
         <v>743</v>
@@ -43324,7 +43323,7 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B297" t="s" s="2">
         <v>749</v>
@@ -43457,13 +43456,13 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>715</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D298" t="s" s="2">
         <v>84</v>
@@ -43488,7 +43487,7 @@
         <v>716</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="M298" t="s" s="2">
         <v>718</v>
@@ -43592,7 +43591,7 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>723</v>
@@ -43725,7 +43724,7 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>724</v>
@@ -43860,7 +43859,7 @@
     </row>
     <row r="301" hidden="true">
       <c r="A301" t="s" s="2">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>725</v>
@@ -43997,7 +43996,7 @@
     </row>
     <row r="302" hidden="true">
       <c r="A302" t="s" s="2">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B302" t="s" s="2">
         <v>730</v>
@@ -44132,7 +44131,7 @@
     </row>
     <row r="303" hidden="true">
       <c r="A303" t="s" s="2">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>736</v>
@@ -44265,7 +44264,7 @@
     </row>
     <row r="304" hidden="true">
       <c r="A304" t="s" s="2">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B304" t="s" s="2">
         <v>805</v>
@@ -44398,7 +44397,7 @@
     </row>
     <row r="305" hidden="true">
       <c r="A305" t="s" s="2">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B305" t="s" s="2">
         <v>807</v>
@@ -44533,7 +44532,7 @@
     </row>
     <row r="306" hidden="true">
       <c r="A306" t="s" s="2">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B306" t="s" s="2">
         <v>809</v>
@@ -44668,7 +44667,7 @@
     </row>
     <row r="307" hidden="true">
       <c r="A307" t="s" s="2">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B307" t="s" s="2">
         <v>809</v>
@@ -44737,7 +44736,7 @@
       </c>
       <c r="Y307" s="2"/>
       <c r="Z307" t="s" s="2">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="AA307" t="s" s="2">
         <v>84</v>
@@ -44805,7 +44804,7 @@
     </row>
     <row r="308" hidden="true">
       <c r="A308" t="s" s="2">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B308" t="s" s="2">
         <v>809</v>
@@ -44874,7 +44873,7 @@
       </c>
       <c r="Y308" s="2"/>
       <c r="Z308" t="s" s="2">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="AA308" t="s" s="2">
         <v>84</v>
@@ -44942,7 +44941,7 @@
     </row>
     <row r="309" hidden="true">
       <c r="A309" t="s" s="2">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B309" t="s" s="2">
         <v>824</v>
@@ -45079,7 +45078,7 @@
     </row>
     <row r="310" hidden="true">
       <c r="A310" t="s" s="2">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B310" t="s" s="2">
         <v>743</v>
@@ -45214,7 +45213,7 @@
     </row>
     <row r="311" hidden="true">
       <c r="A311" t="s" s="2">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B311" t="s" s="2">
         <v>749</v>
@@ -45347,13 +45346,13 @@
     </row>
     <row r="312" hidden="true">
       <c r="A312" t="s" s="2">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>715</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D312" t="s" s="2">
         <v>84</v>
@@ -45378,7 +45377,7 @@
         <v>716</v>
       </c>
       <c r="L312" t="s" s="2">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="M312" t="s" s="2">
         <v>718</v>
@@ -45482,7 +45481,7 @@
     </row>
     <row r="313" hidden="true">
       <c r="A313" t="s" s="2">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>723</v>
@@ -45615,7 +45614,7 @@
     </row>
     <row r="314" hidden="true">
       <c r="A314" t="s" s="2">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>724</v>
@@ -45750,7 +45749,7 @@
     </row>
     <row r="315" hidden="true">
       <c r="A315" t="s" s="2">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B315" t="s" s="2">
         <v>725</v>
@@ -45887,7 +45886,7 @@
     </row>
     <row r="316" hidden="true">
       <c r="A316" t="s" s="2">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B316" t="s" s="2">
         <v>730</v>
@@ -46022,7 +46021,7 @@
     </row>
     <row r="317" hidden="true">
       <c r="A317" t="s" s="2">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B317" t="s" s="2">
         <v>736</v>
@@ -46155,7 +46154,7 @@
     </row>
     <row r="318" hidden="true">
       <c r="A318" t="s" s="2">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B318" t="s" s="2">
         <v>805</v>
@@ -46288,7 +46287,7 @@
     </row>
     <row r="319" hidden="true">
       <c r="A319" t="s" s="2">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B319" t="s" s="2">
         <v>807</v>
@@ -46423,7 +46422,7 @@
     </row>
     <row r="320" hidden="true">
       <c r="A320" t="s" s="2">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B320" t="s" s="2">
         <v>809</v>
@@ -46490,7 +46489,7 @@
       </c>
       <c r="Y320" s="2"/>
       <c r="Z320" t="s" s="2">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AA320" t="s" s="2">
         <v>84</v>
@@ -46558,7 +46557,7 @@
     </row>
     <row r="321" hidden="true">
       <c r="A321" t="s" s="2">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B321" t="s" s="2">
         <v>824</v>
@@ -46695,7 +46694,7 @@
     </row>
     <row r="322" hidden="true">
       <c r="A322" t="s" s="2">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B322" t="s" s="2">
         <v>743</v>
@@ -46830,7 +46829,7 @@
     </row>
     <row r="323" hidden="true">
       <c r="A323" t="s" s="2">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B323" t="s" s="2">
         <v>749</v>
@@ -46963,10 +46962,10 @@
     </row>
     <row r="324" hidden="true">
       <c r="A324" t="s" s="2">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C324" s="2"/>
       <c r="D324" t="s" s="2">
@@ -46989,19 +46988,19 @@
         <v>84</v>
       </c>
       <c r="K324" t="s" s="2">
+        <v>998</v>
+      </c>
+      <c r="L324" t="s" s="2">
         <v>999</v>
       </c>
-      <c r="L324" t="s" s="2">
+      <c r="M324" t="s" s="2">
         <v>1000</v>
       </c>
-      <c r="M324" t="s" s="2">
+      <c r="N324" t="s" s="2">
         <v>1001</v>
       </c>
-      <c r="N324" t="s" s="2">
+      <c r="O324" t="s" s="2">
         <v>1002</v>
-      </c>
-      <c r="O324" t="s" s="2">
-        <v>1003</v>
       </c>
       <c r="P324" t="s" s="2">
         <v>84</v>
@@ -47030,7 +47029,7 @@
       </c>
       <c r="Y324" s="2"/>
       <c r="Z324" t="s" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="AA324" t="s" s="2">
         <v>84</v>
@@ -47048,7 +47047,7 @@
         <v>84</v>
       </c>
       <c r="AF324" t="s" s="2">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AG324" t="s" s="2">
         <v>85</v>
@@ -47084,13 +47083,13 @@
         <v>84</v>
       </c>
       <c r="AR324" t="s" s="2">
+        <v>1004</v>
+      </c>
+      <c r="AS324" t="s" s="2">
         <v>1005</v>
       </c>
-      <c r="AS324" t="s" s="2">
+      <c r="AT324" t="s" s="2">
         <v>1006</v>
-      </c>
-      <c r="AT324" t="s" s="2">
-        <v>1007</v>
       </c>
       <c r="AU324" t="s" s="2">
         <v>84</v>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4301,7 +4301,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>132</v>
       </c>
@@ -6189,7 +6189,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>222</v>
       </c>
@@ -11406,7 +11406,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>321</v>
       </c>
@@ -15287,7 +15287,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>368</v>
       </c>
@@ -19172,7 +19172,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
         <v>413</v>
       </c>
@@ -19579,7 +19579,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
         <v>434</v>
       </c>
@@ -20798,7 +20798,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
         <v>503</v>
       </c>
@@ -23236,7 +23236,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="148" hidden="true">
+    <row r="148">
       <c r="A148" t="s" s="2">
         <v>532</v>
       </c>
@@ -23375,7 +23375,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="149" hidden="true">
+    <row r="149">
       <c r="A149" t="s" s="2">
         <v>540</v>
       </c>
@@ -24187,7 +24187,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="155" hidden="true">
+    <row r="155">
       <c r="A155" t="s" s="2">
         <v>574</v>
       </c>
@@ -24322,7 +24322,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
         <v>584</v>
       </c>
@@ -24590,7 +24590,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="158" hidden="true">
+    <row r="158">
       <c r="A158" t="s" s="2">
         <v>603</v>
       </c>
@@ -26210,7 +26210,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="170" hidden="true">
+    <row r="170">
       <c r="A170" t="s" s="2">
         <v>681</v>
       </c>
@@ -28223,7 +28223,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="185" hidden="true">
+    <row r="185">
       <c r="A185" t="s" s="2">
         <v>759</v>
       </c>
@@ -31703,7 +31703,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="211" hidden="true">
+    <row r="211">
       <c r="A211" t="s" s="2">
         <v>818</v>
       </c>
@@ -31840,7 +31840,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="212" hidden="true">
+    <row r="212">
       <c r="A212" t="s" s="2">
         <v>821</v>
       </c>
@@ -34133,7 +34133,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="229" hidden="true">
+    <row r="229">
       <c r="A229" t="s" s="2">
         <v>861</v>
       </c>
@@ -34270,7 +34270,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="230" hidden="true">
+    <row r="230">
       <c r="A230" t="s" s="2">
         <v>866</v>
       </c>
@@ -34544,7 +34544,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="232" hidden="true">
+    <row r="232">
       <c r="A232" t="s" s="2">
         <v>870</v>
       </c>
@@ -36563,7 +36563,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="247" hidden="true">
+    <row r="247">
       <c r="A247" t="s" s="2">
         <v>892</v>
       </c>
@@ -36700,7 +36700,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="248" hidden="true">
+    <row r="248">
       <c r="A248" t="s" s="2">
         <v>897</v>
       </c>
@@ -46960,7 +46960,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="324" hidden="true">
+    <row r="324">
       <c r="A324" t="s" s="2">
         <v>997</v>
       </c>
@@ -47097,12 +47097,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AU324">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-20T17:15:49+00:00</t>
+    <t>2025-10-21T08:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AU$324</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AU$268</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13902" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11493" uniqueCount="936">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:14:34+00:00</t>
+    <t>2025-10-21T15:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2833,219 +2833,6 @@
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.issuer</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionMedecin</t>
-  </si>
-  <si>
-    <t>savoirFaire/professionMedecin</t>
-  </si>
-  <si>
-    <t>Savoir-faire pour la profession 10 (Médecin)</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionMedecin.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionMedecin.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionMedecin.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionMedecin.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionMedecin.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionMedecin.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionMedecin.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionMedecin.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionMedecin.code.coding:savoirFaire</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionMedecin.code.coding:typeSavoirFaire</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-vs-type-savoir-faire-profession-medecin</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionMedecin.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionMedecin.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionMedecin.issuer</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionPharmacien</t>
-  </si>
-  <si>
-    <t>savoirFaire/professionPharmacien</t>
-  </si>
-  <si>
-    <t>Savoir-faire pour la profession 21 (Pharmacien).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionPharmacien.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionPharmacien.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionPharmacien.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionPharmacien.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionPharmacien.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionPharmacien.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionPharmacien.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionPharmacien.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionPharmacien.code.coding:savoirFaire</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-vs-savoir-faire-profession-pharmacien</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionPharmacien.code.coding:typeSavoirFaire</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-vs-type-savoir-faire-profession-pharmacien</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionPharmacien.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionPharmacien.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionPharmacien.issuer</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionChirurgienDentiste</t>
-  </si>
-  <si>
-    <t>savoirFaire/professionChirurgienDentiste</t>
-  </si>
-  <si>
-    <t>Savoir-faire pour la profession 40 (Chirurgien-Dentiste).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionChirurgienDentiste.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionChirurgienDentiste.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionChirurgienDentiste.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionChirurgienDentiste.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionChirurgienDentiste.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionChirurgienDentiste.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionChirurgienDentiste.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionChirurgienDentiste.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionChirurgienDentiste.code.coding:savoirFaire</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-vs-savoir-faire-profession-chirurgien-dentiste</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionChirurgienDentiste.code.coding:typeSavoirFaire</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-vs-type-savoir-faire-profession-chirurgien-dentiste</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionChirurgienDentiste.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionChirurgienDentiste.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionChirurgienDentiste.issuer</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionInfirmier</t>
-  </si>
-  <si>
-    <t>savoirFaire/professionInfirmier</t>
-  </si>
-  <si>
-    <t>Savoir-faire pour la profession 60 (Infirmier)</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionInfirmier.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionInfirmier.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionInfirmier.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionInfirmier.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionInfirmier.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionInfirmier.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionInfirmier.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionInfirmier.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionInfirmier.code.coding:savoirFaire</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-vs-savoir-faire-profession-infirmier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionInfirmier.code.coding:typeSavoirFaire</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-vs-type-savoir-faire-profession-infirmier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionInfirmier.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionInfirmier.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire/professionInfirmier.issuer</t>
   </si>
   <si>
     <t>Practitioner.qualification:role</t>
@@ -3438,12 +3225,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AU324"/>
+  <dimension ref="A1:AU268"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="82.7265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.71875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="33.1015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="27.65625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -38923,26 +38710,26 @@
         <v>84</v>
       </c>
       <c r="X264" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y264" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="Y264" s="2"/>
       <c r="Z264" t="s" s="2">
-        <v>84</v>
+        <v>922</v>
       </c>
       <c r="AA264" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB264" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AC264" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC264" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD264" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE264" t="s" s="2">
-        <v>814</v>
+        <v>84</v>
       </c>
       <c r="AF264" t="s" s="2">
         <v>815</v>
@@ -38995,14 +38782,12 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="C265" t="s" s="2">
-        <v>881</v>
-      </c>
+        <v>824</v>
+      </c>
+      <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
         <v>84</v>
       </c>
@@ -39023,19 +38808,19 @@
         <v>103</v>
       </c>
       <c r="K265" t="s" s="2">
-        <v>166</v>
+        <v>116</v>
       </c>
       <c r="L265" t="s" s="2">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="M265" t="s" s="2">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="N265" t="s" s="2">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="O265" t="s" s="2">
-        <v>813</v>
+        <v>828</v>
       </c>
       <c r="P265" t="s" s="2">
         <v>84</v>
@@ -39084,13 +38869,13 @@
         <v>84</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>815</v>
+        <v>829</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH265" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI265" t="s" s="2">
         <v>84</v>
@@ -39120,10 +38905,10 @@
         <v>84</v>
       </c>
       <c r="AR265" t="s" s="2">
-        <v>816</v>
+        <v>830</v>
       </c>
       <c r="AS265" t="s" s="2">
-        <v>817</v>
+        <v>831</v>
       </c>
       <c r="AT265" t="s" s="2">
         <v>84</v>
@@ -39134,14 +38919,12 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="C266" t="s" s="2">
-        <v>893</v>
-      </c>
+        <v>743</v>
+      </c>
+      <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
         <v>84</v>
       </c>
@@ -39159,22 +38942,20 @@
         <v>84</v>
       </c>
       <c r="J266" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K266" t="s" s="2">
-        <v>166</v>
+        <v>266</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>810</v>
+        <v>744</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="N266" t="s" s="2">
-        <v>812</v>
-      </c>
+        <v>745</v>
+      </c>
+      <c r="N266" s="2"/>
       <c r="O266" t="s" s="2">
-        <v>813</v>
+        <v>746</v>
       </c>
       <c r="P266" t="s" s="2">
         <v>84</v>
@@ -39199,11 +38980,13 @@
         <v>84</v>
       </c>
       <c r="X266" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y266" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y266" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z266" t="s" s="2">
-        <v>924</v>
+        <v>84</v>
       </c>
       <c r="AA266" t="s" s="2">
         <v>84</v>
@@ -39221,13 +39004,13 @@
         <v>84</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>815</v>
+        <v>743</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH266" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI266" t="s" s="2">
         <v>84</v>
@@ -39257,13 +39040,13 @@
         <v>84</v>
       </c>
       <c r="AR266" t="s" s="2">
-        <v>816</v>
+        <v>84</v>
       </c>
       <c r="AS266" t="s" s="2">
-        <v>817</v>
+        <v>747</v>
       </c>
       <c r="AT266" t="s" s="2">
-        <v>84</v>
+        <v>748</v>
       </c>
       <c r="AU266" t="s" s="2">
         <v>84</v>
@@ -39274,7 +39057,7 @@
         <v>925</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>824</v>
+        <v>749</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -39294,23 +39077,19 @@
         <v>84</v>
       </c>
       <c r="J267" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K267" t="s" s="2">
-        <v>116</v>
+        <v>495</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>825</v>
+        <v>750</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="N267" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="O267" t="s" s="2">
-        <v>828</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="N267" s="2"/>
+      <c r="O267" s="2"/>
       <c r="P267" t="s" s="2">
         <v>84</v>
       </c>
@@ -39358,7 +39137,7 @@
         <v>84</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>829</v>
+        <v>749</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>85</v>
@@ -39394,10 +39173,10 @@
         <v>84</v>
       </c>
       <c r="AR267" t="s" s="2">
-        <v>830</v>
+        <v>84</v>
       </c>
       <c r="AS267" t="s" s="2">
-        <v>831</v>
+        <v>752</v>
       </c>
       <c r="AT267" t="s" s="2">
         <v>84</v>
@@ -39406,12 +39185,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="268" hidden="true">
+    <row r="268">
       <c r="A268" t="s" s="2">
         <v>926</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>743</v>
+        <v>926</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -39422,10 +39201,10 @@
         <v>85</v>
       </c>
       <c r="G268" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H268" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I268" t="s" s="2">
         <v>84</v>
@@ -39434,17 +39213,19 @@
         <v>84</v>
       </c>
       <c r="K268" t="s" s="2">
-        <v>266</v>
+        <v>927</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>744</v>
+        <v>928</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="N268" s="2"/>
+        <v>929</v>
+      </c>
+      <c r="N268" t="s" s="2">
+        <v>930</v>
+      </c>
       <c r="O268" t="s" s="2">
-        <v>746</v>
+        <v>931</v>
       </c>
       <c r="P268" t="s" s="2">
         <v>84</v>
@@ -39469,13 +39250,11 @@
         <v>84</v>
       </c>
       <c r="X268" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y268" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="Y268" s="2"/>
       <c r="Z268" t="s" s="2">
-        <v>84</v>
+        <v>932</v>
       </c>
       <c r="AA268" t="s" s="2">
         <v>84</v>
@@ -39493,13 +39272,13 @@
         <v>84</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>743</v>
+        <v>926</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH268" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI268" t="s" s="2">
         <v>84</v>
@@ -39529,7574 +39308,20 @@
         <v>84</v>
       </c>
       <c r="AR268" t="s" s="2">
-        <v>84</v>
+        <v>933</v>
       </c>
       <c r="AS268" t="s" s="2">
-        <v>747</v>
+        <v>934</v>
       </c>
       <c r="AT268" t="s" s="2">
-        <v>748</v>
+        <v>935</v>
       </c>
       <c r="AU268" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="269" hidden="true">
-      <c r="A269" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="B269" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="C269" s="2"/>
-      <c r="D269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E269" s="2"/>
-      <c r="F269" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G269" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K269" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="L269" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="M269" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="N269" s="2"/>
-      <c r="O269" s="2"/>
-      <c r="P269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q269" s="2"/>
-      <c r="R269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF269" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="AG269" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH269" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ269" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS269" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="AT269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU269" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="270" hidden="true">
-      <c r="A270" t="s" s="2">
-        <v>928</v>
-      </c>
-      <c r="B270" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="C270" t="s" s="2">
-        <v>929</v>
-      </c>
-      <c r="D270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E270" s="2"/>
-      <c r="F270" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G270" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K270" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="L270" t="s" s="2">
-        <v>930</v>
-      </c>
-      <c r="M270" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="N270" s="2"/>
-      <c r="O270" s="2"/>
-      <c r="P270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q270" s="2"/>
-      <c r="R270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF270" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="AG270" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH270" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ270" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ270" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR270" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="AS270" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="AT270" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="AU270" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="271" hidden="true">
-      <c r="A271" t="s" s="2">
-        <v>931</v>
-      </c>
-      <c r="B271" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="C271" s="2"/>
-      <c r="D271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E271" s="2"/>
-      <c r="F271" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G271" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K271" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L271" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M271" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N271" s="2"/>
-      <c r="O271" s="2"/>
-      <c r="P271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q271" s="2"/>
-      <c r="R271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF271" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG271" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH271" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS271" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT271" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU271" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="272" hidden="true">
-      <c r="A272" t="s" s="2">
-        <v>932</v>
-      </c>
-      <c r="B272" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="C272" s="2"/>
-      <c r="D272" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="E272" s="2"/>
-      <c r="F272" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G272" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K272" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="L272" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="M272" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N272" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O272" s="2"/>
-      <c r="P272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q272" s="2"/>
-      <c r="R272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF272" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AG272" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH272" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ272" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS272" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT272" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU272" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="273" hidden="true">
-      <c r="A273" t="s" s="2">
-        <v>933</v>
-      </c>
-      <c r="B273" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="C273" s="2"/>
-      <c r="D273" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="E273" s="2"/>
-      <c r="F273" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G273" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I273" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="J273" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K273" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="L273" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="M273" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="N273" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O273" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="P273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q273" s="2"/>
-      <c r="R273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF273" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="AG273" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH273" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ273" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS273" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AT273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU273" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="274" hidden="true">
-      <c r="A274" t="s" s="2">
-        <v>934</v>
-      </c>
-      <c r="B274" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="C274" s="2"/>
-      <c r="D274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E274" s="2"/>
-      <c r="F274" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G274" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K274" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="L274" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="M274" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N274" s="2"/>
-      <c r="O274" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="P274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q274" s="2"/>
-      <c r="R274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF274" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="AG274" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH274" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ274" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN274" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="AO274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS274" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="AT274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU274" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="275" hidden="true">
-      <c r="A275" t="s" s="2">
-        <v>935</v>
-      </c>
-      <c r="B275" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="C275" s="2"/>
-      <c r="D275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E275" s="2"/>
-      <c r="F275" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="G275" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K275" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="L275" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="M275" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="N275" s="2"/>
-      <c r="O275" s="2"/>
-      <c r="P275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q275" s="2"/>
-      <c r="R275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X275" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y275" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="Z275" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="AA275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF275" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="AG275" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AH275" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ275" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN275" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="AO275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS275" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="AT275" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="AU275" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="276" hidden="true">
-      <c r="A276" t="s" s="2">
-        <v>936</v>
-      </c>
-      <c r="B276" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C276" s="2"/>
-      <c r="D276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E276" s="2"/>
-      <c r="F276" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G276" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K276" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L276" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M276" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N276" s="2"/>
-      <c r="O276" s="2"/>
-      <c r="P276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q276" s="2"/>
-      <c r="R276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF276" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG276" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH276" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS276" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT276" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU276" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="277" hidden="true">
-      <c r="A277" t="s" s="2">
-        <v>937</v>
-      </c>
-      <c r="B277" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="C277" s="2"/>
-      <c r="D277" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="E277" s="2"/>
-      <c r="F277" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G277" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K277" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="L277" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="M277" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N277" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O277" s="2"/>
-      <c r="P277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q277" s="2"/>
-      <c r="R277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB277" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="AC277" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AD277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE277" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AF277" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AG277" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH277" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ277" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS277" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT277" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU277" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="278" hidden="true">
-      <c r="A278" t="s" s="2">
-        <v>938</v>
-      </c>
-      <c r="B278" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="C278" s="2"/>
-      <c r="D278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E278" s="2"/>
-      <c r="F278" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G278" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J278" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K278" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L278" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="M278" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="N278" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="O278" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="P278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q278" s="2"/>
-      <c r="R278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB278" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AC278" s="2"/>
-      <c r="AD278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE278" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="AF278" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="AG278" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH278" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ278" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR278" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="AS278" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="AT278" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU278" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="279" hidden="true">
-      <c r="A279" t="s" s="2">
-        <v>939</v>
-      </c>
-      <c r="B279" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="C279" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="D279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E279" s="2"/>
-      <c r="F279" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G279" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J279" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K279" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L279" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="M279" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="N279" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="O279" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="P279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q279" s="2"/>
-      <c r="R279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X279" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y279" s="2"/>
-      <c r="Z279" t="s" s="2">
-        <v>940</v>
-      </c>
-      <c r="AA279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF279" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="AG279" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH279" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ279" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR279" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="AS279" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="AT279" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU279" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="280" hidden="true">
-      <c r="A280" t="s" s="2">
-        <v>941</v>
-      </c>
-      <c r="B280" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="C280" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="D280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E280" s="2"/>
-      <c r="F280" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G280" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J280" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K280" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L280" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="M280" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="N280" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="O280" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="P280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q280" s="2"/>
-      <c r="R280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X280" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y280" s="2"/>
-      <c r="Z280" t="s" s="2">
-        <v>942</v>
-      </c>
-      <c r="AA280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF280" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="AG280" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH280" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ280" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR280" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="AS280" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="AT280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU280" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="281" hidden="true">
-      <c r="A281" t="s" s="2">
-        <v>943</v>
-      </c>
-      <c r="B281" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="C281" s="2"/>
-      <c r="D281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E281" s="2"/>
-      <c r="F281" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G281" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J281" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K281" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L281" t="s" s="2">
-        <v>825</v>
-      </c>
-      <c r="M281" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="N281" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="O281" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="P281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q281" s="2"/>
-      <c r="R281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF281" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="AG281" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH281" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ281" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR281" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="AS281" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="AT281" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU281" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="282" hidden="true">
-      <c r="A282" t="s" s="2">
-        <v>944</v>
-      </c>
-      <c r="B282" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="C282" s="2"/>
-      <c r="D282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E282" s="2"/>
-      <c r="F282" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G282" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K282" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="L282" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="M282" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="N282" s="2"/>
-      <c r="O282" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="P282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q282" s="2"/>
-      <c r="R282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF282" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="AG282" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH282" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ282" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR282" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS282" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="AT282" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="AU282" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="283" hidden="true">
-      <c r="A283" t="s" s="2">
-        <v>945</v>
-      </c>
-      <c r="B283" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="C283" s="2"/>
-      <c r="D283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E283" s="2"/>
-      <c r="F283" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G283" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K283" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="L283" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="M283" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="N283" s="2"/>
-      <c r="O283" s="2"/>
-      <c r="P283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q283" s="2"/>
-      <c r="R283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF283" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="AG283" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH283" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ283" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS283" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="AT283" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU283" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="284" hidden="true">
-      <c r="A284" t="s" s="2">
-        <v>946</v>
-      </c>
-      <c r="B284" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="C284" t="s" s="2">
-        <v>947</v>
-      </c>
-      <c r="D284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E284" s="2"/>
-      <c r="F284" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G284" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K284" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="L284" t="s" s="2">
-        <v>948</v>
-      </c>
-      <c r="M284" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="N284" s="2"/>
-      <c r="O284" s="2"/>
-      <c r="P284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q284" s="2"/>
-      <c r="R284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF284" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="AG284" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH284" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ284" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ284" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR284" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="AS284" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="AT284" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="AU284" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="285" hidden="true">
-      <c r="A285" t="s" s="2">
-        <v>949</v>
-      </c>
-      <c r="B285" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="C285" s="2"/>
-      <c r="D285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E285" s="2"/>
-      <c r="F285" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G285" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K285" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L285" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M285" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N285" s="2"/>
-      <c r="O285" s="2"/>
-      <c r="P285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q285" s="2"/>
-      <c r="R285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF285" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG285" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH285" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS285" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU285" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="286" hidden="true">
-      <c r="A286" t="s" s="2">
-        <v>950</v>
-      </c>
-      <c r="B286" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="C286" s="2"/>
-      <c r="D286" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="E286" s="2"/>
-      <c r="F286" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G286" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K286" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="L286" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="M286" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N286" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O286" s="2"/>
-      <c r="P286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q286" s="2"/>
-      <c r="R286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF286" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AG286" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH286" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ286" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS286" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU286" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="287" hidden="true">
-      <c r="A287" t="s" s="2">
-        <v>951</v>
-      </c>
-      <c r="B287" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="C287" s="2"/>
-      <c r="D287" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="E287" s="2"/>
-      <c r="F287" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G287" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I287" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="J287" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K287" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="L287" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="M287" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="N287" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O287" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="P287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q287" s="2"/>
-      <c r="R287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF287" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="AG287" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH287" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ287" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS287" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AT287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU287" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="288" hidden="true">
-      <c r="A288" t="s" s="2">
-        <v>952</v>
-      </c>
-      <c r="B288" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="C288" s="2"/>
-      <c r="D288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E288" s="2"/>
-      <c r="F288" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G288" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K288" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="L288" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="M288" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N288" s="2"/>
-      <c r="O288" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="P288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q288" s="2"/>
-      <c r="R288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF288" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="AG288" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH288" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ288" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN288" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="AO288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS288" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="AT288" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU288" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="289" hidden="true">
-      <c r="A289" t="s" s="2">
-        <v>953</v>
-      </c>
-      <c r="B289" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="C289" s="2"/>
-      <c r="D289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E289" s="2"/>
-      <c r="F289" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="G289" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K289" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="L289" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="M289" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="N289" s="2"/>
-      <c r="O289" s="2"/>
-      <c r="P289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q289" s="2"/>
-      <c r="R289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X289" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y289" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="Z289" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="AA289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF289" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="AG289" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AH289" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ289" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN289" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="AO289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR289" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS289" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="AT289" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="AU289" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="290" hidden="true">
-      <c r="A290" t="s" s="2">
-        <v>954</v>
-      </c>
-      <c r="B290" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C290" s="2"/>
-      <c r="D290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E290" s="2"/>
-      <c r="F290" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G290" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K290" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L290" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M290" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N290" s="2"/>
-      <c r="O290" s="2"/>
-      <c r="P290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q290" s="2"/>
-      <c r="R290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF290" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG290" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH290" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS290" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU290" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="291" hidden="true">
-      <c r="A291" t="s" s="2">
-        <v>955</v>
-      </c>
-      <c r="B291" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="C291" s="2"/>
-      <c r="D291" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="E291" s="2"/>
-      <c r="F291" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G291" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K291" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="L291" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="M291" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N291" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O291" s="2"/>
-      <c r="P291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q291" s="2"/>
-      <c r="R291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB291" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="AC291" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AD291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE291" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AF291" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AG291" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH291" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ291" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS291" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU291" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="292" hidden="true">
-      <c r="A292" t="s" s="2">
-        <v>956</v>
-      </c>
-      <c r="B292" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="C292" s="2"/>
-      <c r="D292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E292" s="2"/>
-      <c r="F292" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G292" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J292" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K292" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L292" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="M292" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="N292" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="O292" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="P292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q292" s="2"/>
-      <c r="R292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB292" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AC292" s="2"/>
-      <c r="AD292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE292" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="AF292" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="AG292" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH292" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ292" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR292" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="AS292" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="AT292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU292" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="293" hidden="true">
-      <c r="A293" t="s" s="2">
-        <v>957</v>
-      </c>
-      <c r="B293" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="C293" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="D293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E293" s="2"/>
-      <c r="F293" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G293" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J293" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K293" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L293" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="M293" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="N293" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="O293" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="P293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q293" s="2"/>
-      <c r="R293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X293" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y293" s="2"/>
-      <c r="Z293" t="s" s="2">
-        <v>958</v>
-      </c>
-      <c r="AA293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF293" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="AG293" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH293" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ293" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR293" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="AS293" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="AT293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU293" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="294" hidden="true">
-      <c r="A294" t="s" s="2">
-        <v>959</v>
-      </c>
-      <c r="B294" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="C294" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="D294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E294" s="2"/>
-      <c r="F294" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G294" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J294" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K294" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L294" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="M294" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="N294" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="O294" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="P294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q294" s="2"/>
-      <c r="R294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X294" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y294" s="2"/>
-      <c r="Z294" t="s" s="2">
-        <v>960</v>
-      </c>
-      <c r="AA294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF294" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="AG294" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH294" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ294" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR294" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="AS294" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="AT294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU294" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="295" hidden="true">
-      <c r="A295" t="s" s="2">
-        <v>961</v>
-      </c>
-      <c r="B295" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="C295" s="2"/>
-      <c r="D295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E295" s="2"/>
-      <c r="F295" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G295" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J295" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K295" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L295" t="s" s="2">
-        <v>825</v>
-      </c>
-      <c r="M295" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="N295" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="O295" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="P295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q295" s="2"/>
-      <c r="R295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF295" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="AG295" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH295" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ295" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR295" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="AS295" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="AT295" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU295" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="296" hidden="true">
-      <c r="A296" t="s" s="2">
-        <v>962</v>
-      </c>
-      <c r="B296" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="C296" s="2"/>
-      <c r="D296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E296" s="2"/>
-      <c r="F296" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G296" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K296" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="L296" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="M296" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="N296" s="2"/>
-      <c r="O296" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="P296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q296" s="2"/>
-      <c r="R296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF296" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="AG296" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH296" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ296" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS296" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="AT296" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="AU296" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="297" hidden="true">
-      <c r="A297" t="s" s="2">
-        <v>963</v>
-      </c>
-      <c r="B297" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="C297" s="2"/>
-      <c r="D297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E297" s="2"/>
-      <c r="F297" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G297" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K297" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="L297" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="M297" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="N297" s="2"/>
-      <c r="O297" s="2"/>
-      <c r="P297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q297" s="2"/>
-      <c r="R297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF297" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="AG297" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH297" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ297" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS297" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="AT297" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU297" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="298" hidden="true">
-      <c r="A298" t="s" s="2">
-        <v>964</v>
-      </c>
-      <c r="B298" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="C298" t="s" s="2">
-        <v>965</v>
-      </c>
-      <c r="D298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E298" s="2"/>
-      <c r="F298" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G298" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K298" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="L298" t="s" s="2">
-        <v>966</v>
-      </c>
-      <c r="M298" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="N298" s="2"/>
-      <c r="O298" s="2"/>
-      <c r="P298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q298" s="2"/>
-      <c r="R298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF298" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="AG298" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH298" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ298" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ298" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR298" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="AS298" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="AT298" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="AU298" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="299" hidden="true">
-      <c r="A299" t="s" s="2">
-        <v>967</v>
-      </c>
-      <c r="B299" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="C299" s="2"/>
-      <c r="D299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E299" s="2"/>
-      <c r="F299" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G299" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K299" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L299" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M299" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N299" s="2"/>
-      <c r="O299" s="2"/>
-      <c r="P299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q299" s="2"/>
-      <c r="R299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF299" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG299" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH299" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS299" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT299" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU299" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="300" hidden="true">
-      <c r="A300" t="s" s="2">
-        <v>968</v>
-      </c>
-      <c r="B300" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="C300" s="2"/>
-      <c r="D300" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="E300" s="2"/>
-      <c r="F300" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G300" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K300" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="L300" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="M300" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N300" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O300" s="2"/>
-      <c r="P300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q300" s="2"/>
-      <c r="R300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF300" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AG300" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH300" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ300" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS300" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT300" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU300" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="301" hidden="true">
-      <c r="A301" t="s" s="2">
-        <v>969</v>
-      </c>
-      <c r="B301" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="C301" s="2"/>
-      <c r="D301" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="E301" s="2"/>
-      <c r="F301" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G301" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I301" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="J301" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K301" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="L301" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="M301" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="N301" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O301" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="P301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q301" s="2"/>
-      <c r="R301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF301" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="AG301" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH301" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ301" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS301" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AT301" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU301" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="302" hidden="true">
-      <c r="A302" t="s" s="2">
-        <v>970</v>
-      </c>
-      <c r="B302" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="C302" s="2"/>
-      <c r="D302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E302" s="2"/>
-      <c r="F302" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G302" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K302" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="L302" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="M302" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N302" s="2"/>
-      <c r="O302" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="P302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q302" s="2"/>
-      <c r="R302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF302" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="AG302" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH302" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ302" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN302" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="AO302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS302" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="AT302" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU302" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="303" hidden="true">
-      <c r="A303" t="s" s="2">
-        <v>971</v>
-      </c>
-      <c r="B303" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="C303" s="2"/>
-      <c r="D303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E303" s="2"/>
-      <c r="F303" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="G303" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K303" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="L303" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="M303" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="N303" s="2"/>
-      <c r="O303" s="2"/>
-      <c r="P303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q303" s="2"/>
-      <c r="R303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X303" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y303" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="Z303" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="AA303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF303" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="AG303" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AH303" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ303" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN303" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="AO303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR303" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS303" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="AT303" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="AU303" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="304" hidden="true">
-      <c r="A304" t="s" s="2">
-        <v>972</v>
-      </c>
-      <c r="B304" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C304" s="2"/>
-      <c r="D304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E304" s="2"/>
-      <c r="F304" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G304" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K304" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L304" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M304" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N304" s="2"/>
-      <c r="O304" s="2"/>
-      <c r="P304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q304" s="2"/>
-      <c r="R304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF304" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG304" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH304" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS304" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT304" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU304" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="305" hidden="true">
-      <c r="A305" t="s" s="2">
-        <v>973</v>
-      </c>
-      <c r="B305" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="C305" s="2"/>
-      <c r="D305" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="E305" s="2"/>
-      <c r="F305" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G305" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K305" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="L305" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="M305" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N305" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O305" s="2"/>
-      <c r="P305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q305" s="2"/>
-      <c r="R305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB305" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="AC305" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AD305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE305" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AF305" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AG305" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH305" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ305" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS305" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT305" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU305" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="306" hidden="true">
-      <c r="A306" t="s" s="2">
-        <v>974</v>
-      </c>
-      <c r="B306" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="C306" s="2"/>
-      <c r="D306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E306" s="2"/>
-      <c r="F306" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G306" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J306" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K306" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L306" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="M306" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="N306" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="O306" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="P306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q306" s="2"/>
-      <c r="R306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB306" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AC306" s="2"/>
-      <c r="AD306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE306" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="AF306" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="AG306" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH306" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ306" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR306" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="AS306" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="AT306" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU306" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="307" hidden="true">
-      <c r="A307" t="s" s="2">
-        <v>975</v>
-      </c>
-      <c r="B307" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="C307" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="D307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E307" s="2"/>
-      <c r="F307" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G307" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J307" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K307" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L307" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="M307" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="N307" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="O307" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="P307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q307" s="2"/>
-      <c r="R307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X307" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y307" s="2"/>
-      <c r="Z307" t="s" s="2">
-        <v>976</v>
-      </c>
-      <c r="AA307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF307" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="AG307" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH307" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ307" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR307" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="AS307" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="AT307" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU307" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="308" hidden="true">
-      <c r="A308" t="s" s="2">
-        <v>977</v>
-      </c>
-      <c r="B308" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="C308" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="D308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E308" s="2"/>
-      <c r="F308" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G308" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J308" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K308" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L308" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="M308" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="N308" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="O308" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="P308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q308" s="2"/>
-      <c r="R308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X308" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y308" s="2"/>
-      <c r="Z308" t="s" s="2">
-        <v>978</v>
-      </c>
-      <c r="AA308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF308" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="AG308" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH308" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ308" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR308" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="AS308" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="AT308" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU308" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="309" hidden="true">
-      <c r="A309" t="s" s="2">
-        <v>979</v>
-      </c>
-      <c r="B309" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="C309" s="2"/>
-      <c r="D309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E309" s="2"/>
-      <c r="F309" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G309" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J309" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K309" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L309" t="s" s="2">
-        <v>825</v>
-      </c>
-      <c r="M309" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="N309" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="O309" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="P309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q309" s="2"/>
-      <c r="R309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF309" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="AG309" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH309" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ309" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR309" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="AS309" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="AT309" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU309" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="310" hidden="true">
-      <c r="A310" t="s" s="2">
-        <v>980</v>
-      </c>
-      <c r="B310" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="C310" s="2"/>
-      <c r="D310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E310" s="2"/>
-      <c r="F310" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G310" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K310" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="L310" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="M310" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="N310" s="2"/>
-      <c r="O310" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="P310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q310" s="2"/>
-      <c r="R310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF310" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="AG310" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH310" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ310" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS310" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="AT310" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="AU310" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="311" hidden="true">
-      <c r="A311" t="s" s="2">
-        <v>981</v>
-      </c>
-      <c r="B311" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="C311" s="2"/>
-      <c r="D311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E311" s="2"/>
-      <c r="F311" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G311" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K311" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="L311" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="M311" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="N311" s="2"/>
-      <c r="O311" s="2"/>
-      <c r="P311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q311" s="2"/>
-      <c r="R311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF311" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="AG311" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH311" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ311" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS311" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="AT311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU311" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="312" hidden="true">
-      <c r="A312" t="s" s="2">
-        <v>982</v>
-      </c>
-      <c r="B312" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="C312" t="s" s="2">
-        <v>983</v>
-      </c>
-      <c r="D312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E312" s="2"/>
-      <c r="F312" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G312" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K312" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="L312" t="s" s="2">
-        <v>984</v>
-      </c>
-      <c r="M312" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="N312" s="2"/>
-      <c r="O312" s="2"/>
-      <c r="P312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q312" s="2"/>
-      <c r="R312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF312" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="AG312" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH312" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ312" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR312" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="AS312" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="AT312" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="AU312" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="313" hidden="true">
-      <c r="A313" t="s" s="2">
-        <v>985</v>
-      </c>
-      <c r="B313" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="C313" s="2"/>
-      <c r="D313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E313" s="2"/>
-      <c r="F313" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G313" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K313" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L313" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M313" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N313" s="2"/>
-      <c r="O313" s="2"/>
-      <c r="P313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q313" s="2"/>
-      <c r="R313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF313" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG313" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH313" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS313" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT313" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU313" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="314" hidden="true">
-      <c r="A314" t="s" s="2">
-        <v>986</v>
-      </c>
-      <c r="B314" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="C314" s="2"/>
-      <c r="D314" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="E314" s="2"/>
-      <c r="F314" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G314" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K314" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="L314" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="M314" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N314" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O314" s="2"/>
-      <c r="P314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q314" s="2"/>
-      <c r="R314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF314" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AG314" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH314" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ314" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS314" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT314" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU314" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="315" hidden="true">
-      <c r="A315" t="s" s="2">
-        <v>987</v>
-      </c>
-      <c r="B315" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="C315" s="2"/>
-      <c r="D315" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="E315" s="2"/>
-      <c r="F315" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G315" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I315" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="J315" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K315" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="L315" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="M315" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="N315" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O315" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="P315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q315" s="2"/>
-      <c r="R315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF315" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="AG315" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH315" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ315" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS315" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AT315" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU315" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="316" hidden="true">
-      <c r="A316" t="s" s="2">
-        <v>988</v>
-      </c>
-      <c r="B316" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="C316" s="2"/>
-      <c r="D316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E316" s="2"/>
-      <c r="F316" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G316" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K316" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="L316" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="M316" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N316" s="2"/>
-      <c r="O316" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="P316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q316" s="2"/>
-      <c r="R316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF316" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="AG316" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH316" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ316" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN316" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="AO316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS316" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="AT316" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU316" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="317" hidden="true">
-      <c r="A317" t="s" s="2">
-        <v>989</v>
-      </c>
-      <c r="B317" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="C317" s="2"/>
-      <c r="D317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E317" s="2"/>
-      <c r="F317" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="G317" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K317" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="L317" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="M317" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="N317" s="2"/>
-      <c r="O317" s="2"/>
-      <c r="P317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q317" s="2"/>
-      <c r="R317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X317" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y317" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="Z317" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="AA317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF317" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="AG317" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AH317" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ317" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN317" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="AO317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR317" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS317" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="AT317" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="AU317" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="318" hidden="true">
-      <c r="A318" t="s" s="2">
-        <v>990</v>
-      </c>
-      <c r="B318" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C318" s="2"/>
-      <c r="D318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E318" s="2"/>
-      <c r="F318" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G318" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K318" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L318" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M318" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N318" s="2"/>
-      <c r="O318" s="2"/>
-      <c r="P318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q318" s="2"/>
-      <c r="R318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF318" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG318" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH318" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS318" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT318" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU318" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="319" hidden="true">
-      <c r="A319" t="s" s="2">
-        <v>991</v>
-      </c>
-      <c r="B319" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="C319" s="2"/>
-      <c r="D319" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="E319" s="2"/>
-      <c r="F319" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G319" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K319" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="L319" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="M319" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N319" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O319" s="2"/>
-      <c r="P319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q319" s="2"/>
-      <c r="R319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB319" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="AC319" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AD319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE319" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AF319" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AG319" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH319" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ319" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS319" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AT319" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU319" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="320" hidden="true">
-      <c r="A320" t="s" s="2">
-        <v>992</v>
-      </c>
-      <c r="B320" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="C320" s="2"/>
-      <c r="D320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E320" s="2"/>
-      <c r="F320" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G320" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J320" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K320" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L320" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="M320" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="N320" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="O320" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="P320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q320" s="2"/>
-      <c r="R320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X320" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y320" s="2"/>
-      <c r="Z320" t="s" s="2">
-        <v>993</v>
-      </c>
-      <c r="AA320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF320" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="AG320" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH320" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ320" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR320" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="AS320" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="AT320" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU320" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="321" hidden="true">
-      <c r="A321" t="s" s="2">
-        <v>994</v>
-      </c>
-      <c r="B321" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="C321" s="2"/>
-      <c r="D321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E321" s="2"/>
-      <c r="F321" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G321" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J321" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K321" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L321" t="s" s="2">
-        <v>825</v>
-      </c>
-      <c r="M321" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="N321" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="O321" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="P321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q321" s="2"/>
-      <c r="R321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF321" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="AG321" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH321" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ321" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR321" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="AS321" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="AT321" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU321" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="322" hidden="true">
-      <c r="A322" t="s" s="2">
-        <v>995</v>
-      </c>
-      <c r="B322" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="C322" s="2"/>
-      <c r="D322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E322" s="2"/>
-      <c r="F322" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G322" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K322" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="L322" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="M322" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="N322" s="2"/>
-      <c r="O322" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="P322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q322" s="2"/>
-      <c r="R322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF322" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="AG322" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH322" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ322" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR322" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS322" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="AT322" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="AU322" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="323" hidden="true">
-      <c r="A323" t="s" s="2">
-        <v>996</v>
-      </c>
-      <c r="B323" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="C323" s="2"/>
-      <c r="D323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E323" s="2"/>
-      <c r="F323" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G323" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="H323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K323" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="L323" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="M323" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="N323" s="2"/>
-      <c r="O323" s="2"/>
-      <c r="P323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q323" s="2"/>
-      <c r="R323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF323" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="AG323" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH323" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ323" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS323" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="AT323" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU323" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="s" s="2">
-        <v>997</v>
-      </c>
-      <c r="B324" t="s" s="2">
-        <v>997</v>
-      </c>
-      <c r="C324" s="2"/>
-      <c r="D324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E324" s="2"/>
-      <c r="F324" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G324" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H324" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="I324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K324" t="s" s="2">
-        <v>998</v>
-      </c>
-      <c r="L324" t="s" s="2">
-        <v>999</v>
-      </c>
-      <c r="M324" t="s" s="2">
-        <v>1000</v>
-      </c>
-      <c r="N324" t="s" s="2">
-        <v>1001</v>
-      </c>
-      <c r="O324" t="s" s="2">
-        <v>1002</v>
-      </c>
-      <c r="P324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q324" s="2"/>
-      <c r="R324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X324" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y324" s="2"/>
-      <c r="Z324" t="s" s="2">
-        <v>1003</v>
-      </c>
-      <c r="AA324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF324" t="s" s="2">
-        <v>997</v>
-      </c>
-      <c r="AG324" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH324" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ324" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AK324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ324" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR324" t="s" s="2">
-        <v>1004</v>
-      </c>
-      <c r="AS324" t="s" s="2">
-        <v>1005</v>
-      </c>
-      <c r="AT324" t="s" s="2">
-        <v>1006</v>
-      </c>
-      <c r="AU324" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AU324">
+  <autoFilter ref="A1:AU268">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -47106,7 +39331,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI323">
+  <conditionalFormatting sqref="A2:AI267">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T15:23:03+00:00</t>
+    <t>2025-10-21T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T16:49:23+00:00</t>
+    <t>2025-10-21T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -39,13 +39,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>FrPractitionerDocument</t>
+    <t>FRPractitionerDocument</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Fr Practitioner Document</t>
+    <t>FR Practitioner Document</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T17:18:21+00:00</t>
+    <t>2025-10-22T08:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
